--- a/public/New_Jersey_Expenses.xlsx
+++ b/public/New_Jersey_Expenses.xlsx
@@ -1,32 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\Spectrum Works Projects\career-one-stop-vs-nj-expenses\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cjconti/Documents/Web Design/career-one-stop-vs-nj-expenses/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4EA47E-45B5-4968-86FA-65F9777E4835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720DEF7C-6116-7D4E-8A9B-42A8ECAC642D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15320" yWindow="660" windowWidth="14920" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Appartments" sheetId="1" r:id="rId1"/>
-    <sheet name="Source" sheetId="2" r:id="rId2"/>
+    <sheet name="Apartments" sheetId="1" r:id="rId1"/>
+    <sheet name="Apartments_V2" sheetId="5" r:id="rId2"/>
+    <sheet name="Appartments_Count _V2" sheetId="4" r:id="rId3"/>
+    <sheet name="Appartments_Count" sheetId="3" r:id="rId4"/>
+    <sheet name="Source" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="24">
   <si>
     <t>https://www.apartments.com/rent-market-trends/nj/</t>
   </si>
@@ -51,6 +65,54 @@
   <si>
     <t>Average_Sq_Ft</t>
   </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Min_Cost</t>
+  </si>
+  <si>
+    <t>Max_Cost</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Looked on appartments.com and counted for each type and cost range</t>
+  </si>
+  <si>
+    <t>Percentile</t>
+  </si>
+  <si>
+    <t>Median_Cost</t>
+  </si>
+  <si>
+    <t>New_Count</t>
+  </si>
+  <si>
+    <t>Appartment Counts V2 prevents double counting by counting the total number of appartments. I counted by going from 0 to the max value.</t>
+  </si>
+  <si>
+    <t>Searched_Min_Cost</t>
+  </si>
+  <si>
+    <t>So I searched for 0 to $1000, 0 to $1250, 0 to $1500, all the way up to 0 to $4000.</t>
+  </si>
+  <si>
+    <t>1 Bed 10%</t>
+  </si>
+  <si>
+    <t>1 Bed 25%</t>
+  </si>
+  <si>
+    <t>1 Bed 50%</t>
+  </si>
+  <si>
+    <t>1 Bed 75%</t>
+  </si>
+  <si>
+    <t>1 Bed 90%</t>
+  </si>
 </sst>
 </file>
 
@@ -59,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,16 +129,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -84,18 +167,157 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8"/>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -117,10 +339,69 @@
   <autoFilter ref="A1:C5" xr:uid="{814BDE24-C57C-45A4-987A-7BE2D34849EC}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E36655F9-4C5D-4E2B-B0D8-AA4F8668EE13}" name="Type"/>
-    <tableColumn id="2" xr3:uid="{FE9E6FAC-D577-4885-9B2D-7B5909917B2D}" name="Monthly_Rent" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{FE9E6FAC-D577-4885-9B2D-7B5909917B2D}" name="Monthly_Rent" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{8046BAFD-A553-49C2-97E1-B33C2B6AF181}" name="Average_Sq_Ft"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{14F96CBC-1A32-C24B-B715-37305A517122}" name="Table4" displayName="Table4" ref="A1:B6" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1">
+  <autoFilter ref="A1:B6" xr:uid="{14F96CBC-1A32-C24B-B715-37305A517122}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{05F0E101-A4EF-F04E-B8D5-28715E7AF05D}" name="Type"/>
+    <tableColumn id="2" xr3:uid="{766E8ECA-99C0-8548-8AEC-865958FDF7F6}" name="Monthly_Rent" dataCellStyle="Currency"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6C538D6E-2029-0C42-8680-F57E47FCC793}" name="Table24" displayName="Table24" ref="A1:I27" totalsRowShown="0">
+  <autoFilter ref="A1:I27" xr:uid="{AC11133C-AA73-F94A-A175-5DA20808B242}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{036F99C2-4897-BB4F-97E9-CDB3F11CAE92}" name="ID">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{D134B3DA-E5BE-9748-8964-7502310BCAF9}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{F6148384-9058-0247-B411-173B18CA077A}" name="Searched_Min_Cost" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{F0344193-25FF-8A4A-9DB1-2549C6B7035B}" name="Min_Cost" dataDxfId="3" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{240FB416-BCF2-6147-8F00-877B25C4720E}" name="Max_Cost" dataCellStyle="Currency"/>
+    <tableColumn id="10" xr3:uid="{3D111046-A92C-1F44-8476-8B7A1628DF72}" name="Median_Cost" dataDxfId="2" dataCellStyle="Currency">
+      <calculatedColumnFormula>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{73D50E2E-E335-8243-97E2-B89EEBAE253D}" name="Count"/>
+    <tableColumn id="8" xr3:uid="{CF70B159-4F43-E947-9FD3-7FA7AD1628EA}" name="New_Count" dataDxfId="5">
+      <calculatedColumnFormula>IF(B2&lt;&gt;B1,Table24[[#This Row],[Count]],G2-G1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{97F7CCE9-164E-6F40-AF53-DDA4E85D0186}" name="Percentile" dataDxfId="4" dataCellStyle="Percent">
+      <calculatedColumnFormula>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AC11133C-AA73-F94A-A175-5DA20808B242}" name="Table2" displayName="Table2" ref="A1:G27" totalsRowShown="0">
+  <autoFilter ref="A1:G27" xr:uid="{AC11133C-AA73-F94A-A175-5DA20808B242}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{D9668CFA-70D2-8940-AFB8-51775FA29526}" name="ID">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{F4914CF0-ED72-FD4E-A7E9-39759A9593D8}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{B5AF8381-CAE5-DB43-8CB8-C657004030E6}" name="Min_Cost" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{53EABA3A-EF2C-D547-8A4E-1DA5705B3B0E}" name="Max_Cost" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{616AA817-1C7E-2E41-A0ED-A65C2F439472}" name="Median_Cost" dataDxfId="7" dataCellStyle="Currency">
+      <calculatedColumnFormula>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{9834F28B-0266-474D-92AD-188723CF96D2}" name="Count"/>
+    <tableColumn id="6" xr3:uid="{9CD91225-7096-914A-AFC9-DC97EAE2A07C}" name="Percentile" dataDxfId="6" dataCellStyle="Percent">
+      <calculatedColumnFormula>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -388,13 +669,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -405,7 +686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -416,7 +697,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -427,7 +708,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -438,7 +719,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -458,13 +739,1704 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3693528-17A9-244C-B6B4-BA9A12CE26D2}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4">
+        <v>3000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBED3F3-A741-7D44-A690-008F7F2FF926}">
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F2" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>500</v>
+      </c>
+      <c r="G2">
+        <v>263</v>
+      </c>
+      <c r="H2">
+        <f>IF(B2&lt;&gt;B1,Table24[[#This Row],[Count]],G2-G1)</f>
+        <v>263</v>
+      </c>
+      <c r="I2" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>2.1114322414900449E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <f>ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1250</v>
+      </c>
+      <c r="F3" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1125</v>
+      </c>
+      <c r="G3">
+        <v>587</v>
+      </c>
+      <c r="H3">
+        <f>IF(B3&lt;&gt;B2,Table24[[#This Row],[Count]],G3-G2)</f>
+        <v>324</v>
+      </c>
+      <c r="I3" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>4.7125883108542072E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <f>ROW()-1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1250</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1375</v>
+      </c>
+      <c r="G4">
+        <v>1291</v>
+      </c>
+      <c r="H4">
+        <f>IF(B4&lt;&gt;B3,Table24[[#This Row],[Count]],G4-G3)</f>
+        <v>704</v>
+      </c>
+      <c r="I4" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.10364482980089916</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <f>ROW()-1</f>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1750</v>
+      </c>
+      <c r="F5" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1625</v>
+      </c>
+      <c r="G5">
+        <v>2963</v>
+      </c>
+      <c r="H5">
+        <f>IF(B5&lt;&gt;B4,Table24[[#This Row],[Count]],G5-G4)</f>
+        <v>1672</v>
+      </c>
+      <c r="I5" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.23787732819524726</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <f>ROW()-1</f>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1750</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F6" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1875</v>
+      </c>
+      <c r="G6">
+        <v>5022</v>
+      </c>
+      <c r="H6">
+        <f>IF(B6&lt;&gt;B5,Table24[[#This Row],[Count]],G6-G5)</f>
+        <v>2059</v>
+      </c>
+      <c r="I6" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.40317919075144509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <f>ROW()-1</f>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2250</v>
+      </c>
+      <c r="F7" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2125</v>
+      </c>
+      <c r="G7">
+        <v>6722</v>
+      </c>
+      <c r="H7">
+        <f>IF(B7&lt;&gt;B6,Table24[[#This Row],[Count]],G7-G6)</f>
+        <v>1700</v>
+      </c>
+      <c r="I7" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.53965960179833017</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <f>ROW()-1</f>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2250</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2500</v>
+      </c>
+      <c r="F8" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2375</v>
+      </c>
+      <c r="G8">
+        <v>8607</v>
+      </c>
+      <c r="H8">
+        <f>IF(B8&lt;&gt;B7,Table24[[#This Row],[Count]],G8-G7)</f>
+        <v>1885</v>
+      </c>
+      <c r="I8" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.69099229287090558</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <f>ROW()-1</f>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2750</v>
+      </c>
+      <c r="F9" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2625</v>
+      </c>
+      <c r="G9">
+        <v>9898</v>
+      </c>
+      <c r="H9">
+        <f>IF(B9&lt;&gt;B8,Table24[[#This Row],[Count]],G9-G8)</f>
+        <v>1291</v>
+      </c>
+      <c r="I9" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.79463712267180475</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <f>ROW()-1</f>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2750</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2875</v>
+      </c>
+      <c r="G10">
+        <v>10905</v>
+      </c>
+      <c r="H10">
+        <f>IF(B10&lt;&gt;B9,Table24[[#This Row],[Count]],G10-G9)</f>
+        <v>1007</v>
+      </c>
+      <c r="I10" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.87548169556840072</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f>ROW()-1</f>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3250</v>
+      </c>
+      <c r="F11" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3125</v>
+      </c>
+      <c r="G11">
+        <v>11561</v>
+      </c>
+      <c r="H11">
+        <f>IF(B11&lt;&gt;B10,Table24[[#This Row],[Count]],G11-G10)</f>
+        <v>656</v>
+      </c>
+      <c r="I11" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.92814707771355165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <f>ROW()-1</f>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>3250</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3500</v>
+      </c>
+      <c r="F12" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3375</v>
+      </c>
+      <c r="G12">
+        <v>11932</v>
+      </c>
+      <c r="H12">
+        <f>IF(B12&lt;&gt;B11,Table24[[#This Row],[Count]],G12-G11)</f>
+        <v>371</v>
+      </c>
+      <c r="I12" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.95793192035966601</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <f>ROW()-1</f>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3750</v>
+      </c>
+      <c r="F13" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3625</v>
+      </c>
+      <c r="G13">
+        <v>12192</v>
+      </c>
+      <c r="H13">
+        <f>IF(B13&lt;&gt;B12,Table24[[#This Row],[Count]],G13-G12)</f>
+        <v>260</v>
+      </c>
+      <c r="I13" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.97880539499036612</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <f>ROW()-1</f>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3750</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F14" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3875</v>
+      </c>
+      <c r="G14">
+        <v>12456</v>
+      </c>
+      <c r="H14">
+        <f>IF(B14&lt;&gt;B13,Table24[[#This Row],[Count]],G14-G13)</f>
+        <v>264</v>
+      </c>
+      <c r="I14" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <f t="shared" ref="A15:A27" si="0">ROW()-1</f>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>500</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <f>IF(B15&lt;&gt;B14,Table24[[#This Row],[Count]],G15-G14)</f>
+        <v>10</v>
+      </c>
+      <c r="I15" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>5.6053811659192822E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1250</v>
+      </c>
+      <c r="F16" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1125</v>
+      </c>
+      <c r="G16">
+        <v>52</v>
+      </c>
+      <c r="H16">
+        <f>IF(B16&lt;&gt;B15,Table24[[#This Row],[Count]],G16-G15)</f>
+        <v>42</v>
+      </c>
+      <c r="I16" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>2.914798206278027E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1250</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1375</v>
+      </c>
+      <c r="G17">
+        <v>185</v>
+      </c>
+      <c r="H17">
+        <f>IF(B17&lt;&gt;B16,Table24[[#This Row],[Count]],G17-G16)</f>
+        <v>133</v>
+      </c>
+      <c r="I17" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.10369955156950672</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1750</v>
+      </c>
+      <c r="F18" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1625</v>
+      </c>
+      <c r="G18">
+        <v>306</v>
+      </c>
+      <c r="H18">
+        <f>IF(B18&lt;&gt;B17,Table24[[#This Row],[Count]],G18-G17)</f>
+        <v>121</v>
+      </c>
+      <c r="I18" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.17152466367713004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1750</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F19" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>1875</v>
+      </c>
+      <c r="G19">
+        <v>507</v>
+      </c>
+      <c r="H19">
+        <f>IF(B19&lt;&gt;B18,Table24[[#This Row],[Count]],G19-G18)</f>
+        <v>201</v>
+      </c>
+      <c r="I19" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.28419282511210764</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2250</v>
+      </c>
+      <c r="F20" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2125</v>
+      </c>
+      <c r="G20">
+        <v>806</v>
+      </c>
+      <c r="H20">
+        <f>IF(B20&lt;&gt;B19,Table24[[#This Row],[Count]],G20-G19)</f>
+        <v>299</v>
+      </c>
+      <c r="I20" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.4517937219730942</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2250</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2500</v>
+      </c>
+      <c r="F21" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2375</v>
+      </c>
+      <c r="G21">
+        <v>1134</v>
+      </c>
+      <c r="H21">
+        <f>IF(B21&lt;&gt;B20,Table24[[#This Row],[Count]],G21-G20)</f>
+        <v>328</v>
+      </c>
+      <c r="I21" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.63565022421524664</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2750</v>
+      </c>
+      <c r="F22" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2625</v>
+      </c>
+      <c r="G22">
+        <v>1379</v>
+      </c>
+      <c r="H22">
+        <f>IF(B22&lt;&gt;B21,Table24[[#This Row],[Count]],G22-G21)</f>
+        <v>245</v>
+      </c>
+      <c r="I22" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.77298206278026904</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2750</v>
+      </c>
+      <c r="E23" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F23" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>2875</v>
+      </c>
+      <c r="G23">
+        <v>1510</v>
+      </c>
+      <c r="H23">
+        <f>IF(B23&lt;&gt;B22,Table24[[#This Row],[Count]],G23-G22)</f>
+        <v>131</v>
+      </c>
+      <c r="I23" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.8464125560538116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="4">
+        <v>3250</v>
+      </c>
+      <c r="F24" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3125</v>
+      </c>
+      <c r="G24">
+        <v>1600</v>
+      </c>
+      <c r="H24">
+        <f>IF(B24&lt;&gt;B23,Table24[[#This Row],[Count]],G24-G23)</f>
+        <v>90</v>
+      </c>
+      <c r="I24" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.89686098654708524</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3250</v>
+      </c>
+      <c r="E25" s="4">
+        <v>3500</v>
+      </c>
+      <c r="F25" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3375</v>
+      </c>
+      <c r="G25">
+        <v>1692</v>
+      </c>
+      <c r="H25">
+        <f>IF(B25&lt;&gt;B24,Table24[[#This Row],[Count]],G25-G24)</f>
+        <v>92</v>
+      </c>
+      <c r="I25" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.94843049327354256</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E26" s="4">
+        <v>3750</v>
+      </c>
+      <c r="F26" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3625</v>
+      </c>
+      <c r="G26">
+        <v>1763</v>
+      </c>
+      <c r="H26">
+        <f>IF(B26&lt;&gt;B25,Table24[[#This Row],[Count]],G26-G25)</f>
+        <v>71</v>
+      </c>
+      <c r="I26" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>0.98822869955156956</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4">
+        <v>3750</v>
+      </c>
+      <c r="E27" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F27" s="4">
+        <f>AVERAGE(Table24[[#This Row],[Min_Cost]],Table24[[#This Row],[Max_Cost]])</f>
+        <v>3875</v>
+      </c>
+      <c r="G27">
+        <v>1784</v>
+      </c>
+      <c r="H27">
+        <f>IF(B27&lt;&gt;B26,Table24[[#This Row],[Count]],G27-G26)</f>
+        <v>21</v>
+      </c>
+      <c r="I27" s="5">
+        <f>SUMIFS(Table24[New_Count],Table24[Max_Cost],"&lt;="&amp;Table24[[#This Row],[Max_Cost]],Table24[Type],Table24[[#This Row],[Type]])/SUMIFS(Table24[New_Count],Table24[Type],Table24[[#This Row],[Type]])</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B807FA4-A5A7-5441-A98B-77438ACB73EE}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>500</v>
+      </c>
+      <c r="F2">
+        <v>263</v>
+      </c>
+      <c r="G2" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>1.5828117477130477E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <f>ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1250</v>
+      </c>
+      <c r="E3" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1125</v>
+      </c>
+      <c r="F3">
+        <v>479</v>
+      </c>
+      <c r="G3" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>4.4655753490611461E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <f>ROW()-1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1250</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E4" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1375</v>
+      </c>
+      <c r="F4">
+        <v>947</v>
+      </c>
+      <c r="G4" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.10164901299951853</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <f>ROW()-1</f>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1750</v>
+      </c>
+      <c r="E5" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1625</v>
+      </c>
+      <c r="F5">
+        <v>1912</v>
+      </c>
+      <c r="G5" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.21671882522869523</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <f>ROW()-1</f>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1875</v>
+      </c>
+      <c r="F6">
+        <v>2687</v>
+      </c>
+      <c r="G6" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.37843042850264808</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <f>ROW()-1</f>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2250</v>
+      </c>
+      <c r="E7" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2125</v>
+      </c>
+      <c r="F7">
+        <v>2258</v>
+      </c>
+      <c r="G7" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.51432354357246024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <f>ROW()-1</f>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2250</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E8" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2375</v>
+      </c>
+      <c r="F8">
+        <v>2457</v>
+      </c>
+      <c r="G8" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.66219306692344726</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <f>ROW()-1</f>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2500</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2750</v>
+      </c>
+      <c r="E9" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2625</v>
+      </c>
+      <c r="F9">
+        <v>1669</v>
+      </c>
+      <c r="G9" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.76263842079922961</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <f>ROW()-1</f>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2750</v>
+      </c>
+      <c r="D10" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2875</v>
+      </c>
+      <c r="F10">
+        <v>1403</v>
+      </c>
+      <c r="G10" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.84707510832932109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <f>ROW()-1</f>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D11" s="4">
+        <v>3250</v>
+      </c>
+      <c r="E11" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3125</v>
+      </c>
+      <c r="F11">
+        <v>947</v>
+      </c>
+      <c r="G11" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.90406836783822819</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <f>ROW()-1</f>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3250</v>
+      </c>
+      <c r="D12" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E12" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3375</v>
+      </c>
+      <c r="F12">
+        <v>654</v>
+      </c>
+      <c r="G12" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.94342802118440061</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <f>ROW()-1</f>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3750</v>
+      </c>
+      <c r="E13" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3625</v>
+      </c>
+      <c r="F13">
+        <v>481</v>
+      </c>
+      <c r="G13" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.97237602311025517</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <f>ROW()-1</f>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
+        <v>3750</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E14" s="4">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3875</v>
+      </c>
+      <c r="F14">
+        <v>459</v>
+      </c>
+      <c r="G14" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <f t="shared" ref="A15:A27" si="0">ROW()-1</f>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>500</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>4.3687199650502403E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1250</v>
+      </c>
+      <c r="E16" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1125</v>
+      </c>
+      <c r="F16">
+        <v>42</v>
+      </c>
+      <c r="G16" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>2.2717343818261248E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1250</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1375</v>
+      </c>
+      <c r="F17">
+        <v>151</v>
+      </c>
+      <c r="G17" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>8.8685015290519878E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1500</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1750</v>
+      </c>
+      <c r="E18" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1625</v>
+      </c>
+      <c r="F18">
+        <v>142</v>
+      </c>
+      <c r="G18" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.15072083879423329</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E19" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>1875</v>
+      </c>
+      <c r="F19">
+        <v>225</v>
+      </c>
+      <c r="G19" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.24901703800786371</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2250</v>
+      </c>
+      <c r="E20" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2125</v>
+      </c>
+      <c r="F20">
+        <v>374</v>
+      </c>
+      <c r="G20" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.41240716470074268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2250</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2375</v>
+      </c>
+      <c r="F21">
+        <v>390</v>
+      </c>
+      <c r="G21" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.58278724333770204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2500</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2750</v>
+      </c>
+      <c r="E22" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2625</v>
+      </c>
+      <c r="F22">
+        <v>287</v>
+      </c>
+      <c r="G22" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.70816950633464393</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2750</v>
+      </c>
+      <c r="D23" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>2875</v>
+      </c>
+      <c r="F23">
+        <v>190</v>
+      </c>
+      <c r="G23" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.79117518567059852</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D24" s="4">
+        <v>3250</v>
+      </c>
+      <c r="E24" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3125</v>
+      </c>
+      <c r="F24">
+        <v>155</v>
+      </c>
+      <c r="G24" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.85889034512887719</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3250</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3500</v>
+      </c>
+      <c r="E25" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3375</v>
+      </c>
+      <c r="F25">
+        <v>153</v>
+      </c>
+      <c r="G25" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.92573176059414597</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3500</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3750</v>
+      </c>
+      <c r="E26" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3625</v>
+      </c>
+      <c r="F26">
+        <v>120</v>
+      </c>
+      <c r="G26" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>0.97815640017474881</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3750</v>
+      </c>
+      <c r="D27" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E27" s="6">
+        <f>AVERAGE(Table2[[#This Row],[Min_Cost]],Table2[[#This Row],[Max_Cost]])</f>
+        <v>3875</v>
+      </c>
+      <c r="F27">
+        <v>50</v>
+      </c>
+      <c r="G27" s="5">
+        <f>SUMIFS(Table2[Count],Table2[Max_Cost],"&lt;="&amp;Table2[[#This Row],[Max_Cost]],Table2[Type],Table2[[#This Row],[Type]])/SUMIFS(Table2[Count],Table2[Type],Table2[[#This Row],[Type]])</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15F3614-652C-4B5F-91A9-D75409CD994E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/public/New_Jersey_Expenses.xlsx
+++ b/public/New_Jersey_Expenses.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720DEF7C-6116-7D4E-8A9B-42A8ECAC642D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15320" yWindow="660" windowWidth="14920" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14180" yWindow="4140" windowWidth="16060" windowHeight="13700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Apartments" sheetId="1" r:id="rId1"/>
